--- a/data/sejours.xlsx
+++ b/data/sejours.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,11 +469,6 @@
           <t>motif</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>praticien</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -514,11 +509,6 @@
           <t>Décompensation cardiaque globale</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Dr Martin</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -559,11 +549,6 @@
           <t>Bilan de douleur thoracique d'effort</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Dr Martin</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -604,11 +589,6 @@
           <t>Pneumopathie aiguë communautaire</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Dr Nguyen</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -649,11 +629,6 @@
           <t>Pneumopathie aiguë communautaire (épisode antérieur)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Dr Nguyen</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -694,11 +669,6 @@
           <t>Prothèse totale de hanche droite</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Dr Lefevre</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -737,11 +707,6 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>Bilan pré-opératoire prothèse de hanche</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Dr Lefevre</t>
         </is>
       </c>
     </row>

--- a/data/sejours.xlsx
+++ b/data/sejours.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,37 +436,27 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>sejour_key</t>
+          <t>ordre</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ordre</t>
+          <t>id_sejour</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>id_sejour</t>
+          <t>service</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>entree</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>entree</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
           <t>sortie</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>motif</t>
         </is>
       </c>
     </row>
@@ -476,37 +466,27 @@
           <t>REC-2024-00187</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>sej1</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+      <c r="B2" t="n">
         <v>0</v>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ID0000123</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ID0000123</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
           <t>2024-05-14</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Décompensation cardiaque globale</t>
         </is>
       </c>
     </row>
@@ -516,37 +496,27 @@
           <t>REC-2024-00187</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>sej0</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+      <c r="B3" t="n">
         <v>1</v>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ID0000098</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ID0000098</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2023-11-10</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
           <t>2023-11-13</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Bilan de douleur thoracique d'effort</t>
         </is>
       </c>
     </row>
@@ -556,37 +526,27 @@
           <t>REC-2024-00099</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>sej1</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+      <c r="B4" t="n">
         <v>0</v>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ID0000201</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ID0000201</t>
+          <t>Pneumologie</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pneumologie</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2024-04-10</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
           <t>2024-04-16</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Pneumopathie aiguë communautaire</t>
         </is>
       </c>
     </row>
@@ -596,37 +556,27 @@
           <t>REC-2024-00099</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>sej0</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+      <c r="B5" t="n">
         <v>1</v>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ID0000077</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ID0000077</t>
+          <t>Pneumologie</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pneumologie</t>
+          <t>2023-03-05</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
           <t>2023-03-09</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Pneumopathie aiguë communautaire (épisode antérieur)</t>
         </is>
       </c>
     </row>
@@ -636,37 +586,27 @@
           <t>REC-2024-00234</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>sej1</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
+      <c r="B6" t="n">
         <v>0</v>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ID0000156</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ID0000156</t>
+          <t>Chirurgie orthopédique</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chirurgie orthopédique</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Prothèse totale de hanche droite</t>
         </is>
       </c>
     </row>
@@ -676,37 +616,27 @@
           <t>REC-2024-00234</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>sej0</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+      <c r="B7" t="n">
         <v>1</v>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ID0000142</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ID0000142</t>
+          <t>Chirurgie orthopédique</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chirurgie orthopédique</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2024-05-15</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2024-05-15</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Bilan pré-opératoire prothèse de hanche</t>
         </is>
       </c>
     </row>
